--- a/demo_data/TB_LIST.xlsx
+++ b/demo_data/TB_LIST.xlsx
@@ -683,12 +683,12 @@
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>IW510+</t>
+          <t>IW564+</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>IW510</t>
+          <t>IW564</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -700,12 +700,12 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>IW530+</t>
+          <t>IW638+</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>IW530</t>
+          <t>IW638</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -717,12 +717,12 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>IW552+</t>
+          <t>IW768+</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>IW552</t>
+          <t>IW768</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
@@ -734,29 +734,29 @@
       <c r="T4" s="7" t="n"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>IW552+</t>
+          <t>IW820+</t>
         </is>
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>IW552</t>
+          <t>IW820</t>
         </is>
       </c>
       <c r="W4" s="7" t="inlineStr">
         <is>
-          <t>LIT-2005</t>
+          <t>TIT-1008</t>
         </is>
       </c>
       <c r="X4" s="7" t="n"/>
       <c r="Z4" s="7" t="n"/>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>IW564+</t>
+          <t>IW888+</t>
         </is>
       </c>
       <c r="AB4" s="7" t="inlineStr">
         <is>
-          <t>IW564</t>
+          <t>IW888</t>
         </is>
       </c>
       <c r="AC4" s="7" t="inlineStr">
@@ -768,12 +768,12 @@
       <c r="AF4" s="7" t="n"/>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>IW570+</t>
+          <t>IW948+</t>
         </is>
       </c>
       <c r="AH4" s="7" t="inlineStr">
         <is>
-          <t>IW570</t>
+          <t>IW948</t>
         </is>
       </c>
       <c r="AI4" s="7" t="inlineStr">
@@ -785,12 +785,12 @@
       <c r="AL4" s="7" t="n"/>
       <c r="AM4" s="7" t="inlineStr">
         <is>
-          <t>IW586+</t>
+          <t>IW1018+</t>
         </is>
       </c>
       <c r="AN4" s="7" t="inlineStr">
         <is>
-          <t>IW586</t>
+          <t>IW1018</t>
         </is>
       </c>
       <c r="AO4" s="7" t="inlineStr">
@@ -804,12 +804,12 @@
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>IW512+</t>
+          <t>IW566+</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>IW512</t>
+          <t>IW566</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -821,12 +821,12 @@
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>IW532+</t>
+          <t>IW640+</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>IW532</t>
+          <t>IW640</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -838,29 +838,29 @@
       <c r="T5" s="7" t="n"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>IW552+</t>
+          <t>IW822+</t>
         </is>
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>IW552</t>
+          <t>IW822</t>
         </is>
       </c>
       <c r="W5" s="7" t="inlineStr">
         <is>
-          <t>TIT-1008</t>
+          <t>LIT-2005</t>
         </is>
       </c>
       <c r="X5" s="7" t="n"/>
       <c r="Z5" s="7" t="n"/>
       <c r="AA5" s="7" t="inlineStr">
         <is>
-          <t>IW566+</t>
+          <t>IW890+</t>
         </is>
       </c>
       <c r="AB5" s="7" t="inlineStr">
         <is>
-          <t>IW566</t>
+          <t>IW890</t>
         </is>
       </c>
       <c r="AC5" s="7" t="inlineStr">
@@ -872,12 +872,12 @@
       <c r="AF5" s="7" t="n"/>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>IW582+</t>
+          <t>IW960+</t>
         </is>
       </c>
       <c r="AH5" s="7" t="inlineStr">
         <is>
-          <t>IW582</t>
+          <t>IW960</t>
         </is>
       </c>
       <c r="AI5" s="7" t="inlineStr">
@@ -889,12 +889,12 @@
       <c r="AL5" s="7" t="n"/>
       <c r="AM5" s="7" t="inlineStr">
         <is>
-          <t>IW594+</t>
+          <t>IW1026+</t>
         </is>
       </c>
       <c r="AN5" s="7" t="inlineStr">
         <is>
-          <t>IW594</t>
+          <t>IW1026</t>
         </is>
       </c>
       <c r="AO5" s="7" t="inlineStr">
@@ -908,12 +908,12 @@
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>IW514+</t>
+          <t>IW568+</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>IW514</t>
+          <t>IW568</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -925,12 +925,12 @@
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>IW534+</t>
+          <t>IW642+</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>IW534</t>
+          <t>IW642</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -942,12 +942,12 @@
       <c r="T6" s="7" t="n"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
-          <t>IW558+</t>
+          <t>IW828+</t>
         </is>
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>IW558</t>
+          <t>IW828</t>
         </is>
       </c>
       <c r="W6" s="7" t="inlineStr">
@@ -961,29 +961,29 @@
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>IW514+</t>
+          <t>IW570+</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>IW514</t>
+          <t>IW570</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>LIT-02A</t>
+          <t>AIT-4005</t>
         </is>
       </c>
       <c r="F7" s="7" t="n"/>
       <c r="T7" s="7" t="n"/>
       <c r="U7" s="7" t="inlineStr">
         <is>
-          <t>IW564+</t>
+          <t>IW834+</t>
         </is>
       </c>
       <c r="V7" s="7" t="inlineStr">
         <is>
-          <t>IW564</t>
+          <t>IW834</t>
         </is>
       </c>
       <c r="W7" s="7" t="inlineStr">
@@ -997,17 +997,17 @@
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>IW516+</t>
+          <t>IW572+</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>IW516</t>
+          <t>IW572</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>AIT-4005</t>
+          <t>LIT-02A</t>
         </is>
       </c>
       <c r="F8" s="7" t="n"/>
@@ -1016,17 +1016,17 @@
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>IW516+</t>
+          <t>IW574+</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>IW516</t>
+          <t>IW574</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>LIT-02B</t>
+          <t>PIT-3007</t>
         </is>
       </c>
       <c r="F9" s="7" t="n"/>
@@ -1035,17 +1035,17 @@
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>IW520+</t>
+          <t>IW576+</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>IW520</t>
+          <t>IW576</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>PIT-3007</t>
+          <t>AIT-2011</t>
         </is>
       </c>
       <c r="F10" s="7" t="n"/>
@@ -1054,17 +1054,17 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>IW522+</t>
+          <t>IW578+</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>IW522</t>
+          <t>IW578</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>AIT-2011</t>
+          <t>LIT-02B</t>
         </is>
       </c>
       <c r="F11" s="7" t="n"/>
@@ -1321,12 +1321,12 @@
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>IW514+</t>
+          <t>IW2616+</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>IW514</t>
+          <t>IW2616</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1338,12 +1338,12 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>IW520+</t>
+          <t>IW2676+</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>IW520</t>
+          <t>IW2676</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1355,12 +1355,12 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>IW532+</t>
+          <t>IW2742+</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>IW532</t>
+          <t>IW2742</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
@@ -1372,12 +1372,12 @@
       <c r="T4" s="7" t="n"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>IW550+</t>
+          <t>IW2814+</t>
         </is>
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>IW550</t>
+          <t>IW2814</t>
         </is>
       </c>
       <c r="W4" s="7" t="inlineStr">
@@ -1389,29 +1389,29 @@
       <c r="Z4" s="7" t="n"/>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>IW554+</t>
+          <t>IW2868+</t>
         </is>
       </c>
       <c r="AB4" s="7" t="inlineStr">
         <is>
-          <t>IW554</t>
+          <t>IW2868</t>
         </is>
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
-          <t>AIT-1009</t>
+          <t>PIT-7003</t>
         </is>
       </c>
       <c r="AD4" s="7" t="n"/>
       <c r="AF4" s="7" t="n"/>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>IW568+</t>
+          <t>IW2940+</t>
         </is>
       </c>
       <c r="AH4" s="7" t="inlineStr">
         <is>
-          <t>IW568</t>
+          <t>IW2940</t>
         </is>
       </c>
       <c r="AI4" s="7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       <c r="AL4" s="7" t="n"/>
       <c r="AM4" s="7" t="inlineStr">
         <is>
-          <t>IW570+</t>
+          <t>IW2996+</t>
         </is>
       </c>
       <c r="AN4" s="7" t="inlineStr">
         <is>
-          <t>IW570</t>
+          <t>IW2996</t>
         </is>
       </c>
       <c r="AO4" s="7" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AR4" s="7" t="n"/>
       <c r="AS4" s="7" t="inlineStr">
         <is>
-          <t>IW582+</t>
+          <t>IW3062+</t>
         </is>
       </c>
       <c r="AT4" s="7" t="inlineStr">
         <is>
-          <t>IW582</t>
+          <t>IW3062</t>
         </is>
       </c>
       <c r="AU4" s="7" t="inlineStr">
@@ -1459,12 +1459,12 @@
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>IW524+</t>
+          <t>IW2680+</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>IW524</t>
+          <t>IW2680</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1476,12 +1476,12 @@
       <c r="N5" s="7" t="n"/>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>IW534+</t>
+          <t>IW2744+</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>IW534</t>
+          <t>IW2744</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -1493,12 +1493,12 @@
       <c r="T5" s="7" t="n"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>IW552+</t>
+          <t>IW2816+</t>
         </is>
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>IW552</t>
+          <t>IW2816</t>
         </is>
       </c>
       <c r="W5" s="7" t="inlineStr">
@@ -1510,29 +1510,29 @@
       <c r="Z5" s="7" t="n"/>
       <c r="AA5" s="7" t="inlineStr">
         <is>
-          <t>IW560+</t>
+          <t>IW2872+</t>
         </is>
       </c>
       <c r="AB5" s="7" t="inlineStr">
         <is>
-          <t>IW560</t>
+          <t>IW2872</t>
         </is>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
-          <t>PIT-6008</t>
+          <t>AIT-1009</t>
         </is>
       </c>
       <c r="AD5" s="7" t="n"/>
       <c r="AF5" s="7" t="n"/>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>IW572+</t>
+          <t>IW2944+</t>
         </is>
       </c>
       <c r="AH5" s="7" t="inlineStr">
         <is>
-          <t>IW572</t>
+          <t>IW2944</t>
         </is>
       </c>
       <c r="AI5" s="7" t="inlineStr">
@@ -1544,12 +1544,12 @@
       <c r="AL5" s="7" t="n"/>
       <c r="AM5" s="7" t="inlineStr">
         <is>
-          <t>IW582+</t>
+          <t>IW3008+</t>
         </is>
       </c>
       <c r="AN5" s="7" t="inlineStr">
         <is>
-          <t>IW582</t>
+          <t>IW3008</t>
         </is>
       </c>
       <c r="AO5" s="7" t="inlineStr">
@@ -1561,12 +1561,12 @@
       <c r="AR5" s="7" t="n"/>
       <c r="AS5" s="7" t="inlineStr">
         <is>
-          <t>IW588+</t>
+          <t>IW3068+</t>
         </is>
       </c>
       <c r="AT5" s="7" t="inlineStr">
         <is>
-          <t>IW588</t>
+          <t>IW3068</t>
         </is>
       </c>
       <c r="AU5" s="7" t="inlineStr">
@@ -1580,12 +1580,12 @@
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>IW526+</t>
+          <t>IW2682+</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>IW526</t>
+          <t>IW2682</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1597,12 +1597,12 @@
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>IW540+</t>
+          <t>IW2750+</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>IW540</t>
+          <t>IW2750</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
@@ -1614,12 +1614,12 @@
       <c r="T6" s="7" t="n"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
-          <t>IW554+</t>
+          <t>IW2818+</t>
         </is>
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>IW554</t>
+          <t>IW2818</t>
         </is>
       </c>
       <c r="W6" s="7" t="inlineStr">
@@ -1631,29 +1631,29 @@
       <c r="Z6" s="7" t="n"/>
       <c r="AA6" s="7" t="inlineStr">
         <is>
-          <t>IW562+</t>
+          <t>IW2878+</t>
         </is>
       </c>
       <c r="AB6" s="7" t="inlineStr">
         <is>
-          <t>IW562</t>
+          <t>IW2878</t>
         </is>
       </c>
       <c r="AC6" s="7" t="inlineStr">
         <is>
-          <t>AIT-5002</t>
+          <t>PIT-6008</t>
         </is>
       </c>
       <c r="AD6" s="7" t="n"/>
       <c r="AR6" s="7" t="n"/>
       <c r="AS6" s="7" t="inlineStr">
         <is>
-          <t>IW592+</t>
+          <t>IW3072+</t>
         </is>
       </c>
       <c r="AT6" s="7" t="inlineStr">
         <is>
-          <t>IW592</t>
+          <t>IW3072</t>
         </is>
       </c>
       <c r="AU6" s="7" t="inlineStr">
@@ -1667,17 +1667,17 @@
       <c r="Z7" s="7" t="n"/>
       <c r="AA7" s="7" t="inlineStr">
         <is>
-          <t>IW562+</t>
+          <t>IW2880+</t>
         </is>
       </c>
       <c r="AB7" s="7" t="inlineStr">
         <is>
-          <t>IW562</t>
+          <t>IW2880</t>
         </is>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
-          <t>PIT-7003</t>
+          <t>AIT-5002</t>
         </is>
       </c>
       <c r="AD7" s="7" t="n"/>
@@ -1853,12 +1853,12 @@
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>IW530+</t>
+          <t>IW4734+</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>IW530</t>
+          <t>IW4734</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1870,12 +1870,12 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>IW544+</t>
+          <t>IW4802+</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>IW544</t>
+          <t>IW4802</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1887,12 +1887,12 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>IW540+</t>
+          <t>IW4852+</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>IW540</t>
+          <t>IW4852</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
@@ -1904,12 +1904,12 @@
       <c r="T4" s="7" t="n"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>IW560+</t>
+          <t>IW4926+</t>
         </is>
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>IW560</t>
+          <t>IW4926</t>
         </is>
       </c>
       <c r="W4" s="7" t="inlineStr">
@@ -1921,17 +1921,17 @@
       <c r="Z4" s="7" t="n"/>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>IW572+</t>
+          <t>IW4980+</t>
         </is>
       </c>
       <c r="AB4" s="7" t="inlineStr">
         <is>
-          <t>IW572</t>
+          <t>IW4980</t>
         </is>
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
-          <t>AIT-5008</t>
+          <t>AIT-7005</t>
         </is>
       </c>
       <c r="AD4" s="7" t="n"/>
@@ -1940,12 +1940,12 @@
       <c r="T5" s="7" t="n"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>IW564+</t>
+          <t>IW4930+</t>
         </is>
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>IW564</t>
+          <t>IW4930</t>
         </is>
       </c>
       <c r="W5" s="7" t="inlineStr">
@@ -1957,17 +1957,17 @@
       <c r="Z5" s="7" t="n"/>
       <c r="AA5" s="7" t="inlineStr">
         <is>
-          <t>IW572+</t>
+          <t>IW4992+</t>
         </is>
       </c>
       <c r="AB5" s="7" t="inlineStr">
         <is>
-          <t>IW572</t>
+          <t>IW4992</t>
         </is>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
-          <t>AIT-7005</t>
+          <t>AIT-5008</t>
         </is>
       </c>
       <c r="AD5" s="7" t="n"/>
@@ -2088,7 +2088,7 @@
     <row r="4">
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6209</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -2105,7 +2105,7 @@
       <c r="F4" s="7" t="n"/>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>N021</t>
+          <t>N6273</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="L4" s="7" t="n"/>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>N031</t>
+          <t>N6337</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="5">
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6210</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -2160,7 +2160,7 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6211</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6212</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6213</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -2217,7 +2217,7 @@
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6214</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6215</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="11">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6216</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -2274,7 +2274,7 @@
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6217</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2293,7 +2293,7 @@
     <row r="13">
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6218</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -2312,7 +2312,7 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6219</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="15">
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6220</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6221</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6222</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2388,7 +2388,7 @@
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6223</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -2407,7 +2407,7 @@
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6224</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -2426,7 +2426,7 @@
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6225</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -2445,7 +2445,7 @@
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6226</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -2464,7 +2464,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6227</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6228</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6229</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="25">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N6230</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -2762,12 +2762,12 @@
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>IW512+</t>
+          <t>IW180790+</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>IW512</t>
+          <t>IW180790</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2779,12 +2779,12 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>IW532+</t>
+          <t>IW180918+</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>IW532</t>
+          <t>IW180918</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -2796,29 +2796,29 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>IW548+</t>
+          <t>IW180980+</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>IW548</t>
+          <t>IW180980</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>AIT-7002</t>
+          <t>AIT-3009</t>
         </is>
       </c>
       <c r="R4" s="7" t="n"/>
       <c r="T4" s="7" t="n"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>IW560+</t>
+          <t>IW181054+</t>
         </is>
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>IW560</t>
+          <t>IW181054</t>
         </is>
       </c>
       <c r="W4" s="7" t="inlineStr">
@@ -2830,12 +2830,12 @@
       <c r="Z4" s="7" t="n"/>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>IW572+</t>
+          <t>IW181120+</t>
         </is>
       </c>
       <c r="AB4" s="7" t="inlineStr">
         <is>
-          <t>IW572</t>
+          <t>IW181120</t>
         </is>
       </c>
       <c r="AC4" s="7" t="inlineStr">
@@ -2847,12 +2847,12 @@
       <c r="AF4" s="7" t="n"/>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>IW582+</t>
+          <t>IW181184+</t>
         </is>
       </c>
       <c r="AH4" s="7" t="inlineStr">
         <is>
-          <t>IW582</t>
+          <t>IW181184</t>
         </is>
       </c>
       <c r="AI4" s="7" t="inlineStr">
@@ -2864,12 +2864,12 @@
       <c r="AL4" s="7" t="n"/>
       <c r="AM4" s="7" t="inlineStr">
         <is>
-          <t>IW580+</t>
+          <t>IW181236+</t>
         </is>
       </c>
       <c r="AN4" s="7" t="inlineStr">
         <is>
-          <t>IW580</t>
+          <t>IW181236</t>
         </is>
       </c>
       <c r="AO4" s="7" t="inlineStr">
@@ -2883,12 +2883,12 @@
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>IW538+</t>
+          <t>IW180924+</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>IW538</t>
+          <t>IW180924</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -2900,29 +2900,29 @@
       <c r="N5" s="7" t="n"/>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>IW548+</t>
+          <t>IW180988+</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>IW548</t>
+          <t>IW180988</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>AIT-3009</t>
+          <t>AIT-7002</t>
         </is>
       </c>
       <c r="R5" s="7" t="n"/>
       <c r="AF5" s="7" t="n"/>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>IW584+</t>
+          <t>IW181186+</t>
         </is>
       </c>
       <c r="AH5" s="7" t="inlineStr">
         <is>
-          <t>IW584</t>
+          <t>IW181186</t>
         </is>
       </c>
       <c r="AI5" s="7" t="inlineStr">
@@ -2934,12 +2934,12 @@
       <c r="AL5" s="7" t="n"/>
       <c r="AM5" s="7" t="inlineStr">
         <is>
-          <t>IW580+</t>
+          <t>IW181238+</t>
         </is>
       </c>
       <c r="AN5" s="7" t="inlineStr">
         <is>
-          <t>IW580</t>
+          <t>IW181238</t>
         </is>
       </c>
       <c r="AO5" s="7" t="inlineStr">
@@ -2953,12 +2953,12 @@
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>IW552+</t>
+          <t>IW180992+</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>IW552</t>
+          <t>IW180992</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
@@ -2970,12 +2970,12 @@
       <c r="AL6" s="7" t="n"/>
       <c r="AM6" s="7" t="inlineStr">
         <is>
-          <t>IW586+</t>
+          <t>IW181242+</t>
         </is>
       </c>
       <c r="AN6" s="7" t="inlineStr">
         <is>
-          <t>IW586</t>
+          <t>IW181242</t>
         </is>
       </c>
       <c r="AO6" s="7" t="inlineStr">
@@ -2989,12 +2989,12 @@
       <c r="AL7" s="7" t="n"/>
       <c r="AM7" s="7" t="inlineStr">
         <is>
-          <t>IW588+</t>
+          <t>IW181244+</t>
         </is>
       </c>
       <c r="AN7" s="7" t="inlineStr">
         <is>
-          <t>IW588</t>
+          <t>IW181244</t>
         </is>
       </c>
       <c r="AO7" s="7" t="inlineStr">
@@ -3008,12 +3008,12 @@
       <c r="AL8" s="7" t="n"/>
       <c r="AM8" s="7" t="inlineStr">
         <is>
-          <t>IW594+</t>
+          <t>IW181250+</t>
         </is>
       </c>
       <c r="AN8" s="7" t="inlineStr">
         <is>
-          <t>IW594</t>
+          <t>IW181250</t>
         </is>
       </c>
       <c r="AO8" s="7" t="inlineStr">
@@ -3221,12 +3221,12 @@
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>IW520+</t>
+          <t>IW197236+</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>IW520</t>
+          <t>IW197236</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -3238,12 +3238,12 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>IW534+</t>
+          <t>IW197304+</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>IW534</t>
+          <t>IW197304</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -3255,12 +3255,12 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>IW542+</t>
+          <t>IW197366+</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>IW542</t>
+          <t>IW197366</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
@@ -3272,12 +3272,12 @@
       <c r="T4" s="7" t="n"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>IW554+</t>
+          <t>IW197432+</t>
         </is>
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>IW554</t>
+          <t>IW197432</t>
         </is>
       </c>
       <c r="W4" s="7" t="inlineStr">
@@ -3289,12 +3289,12 @@
       <c r="Z4" s="7" t="n"/>
       <c r="AA4" s="7" t="inlineStr">
         <is>
-          <t>IW570+</t>
+          <t>IW197502+</t>
         </is>
       </c>
       <c r="AB4" s="7" t="inlineStr">
         <is>
-          <t>IW570</t>
+          <t>IW197502</t>
         </is>
       </c>
       <c r="AC4" s="7" t="inlineStr">
@@ -3306,12 +3306,12 @@
       <c r="AF4" s="7" t="n"/>
       <c r="AG4" s="7" t="inlineStr">
         <is>
-          <t>IW582+</t>
+          <t>IW197622+</t>
         </is>
       </c>
       <c r="AH4" s="7" t="inlineStr">
         <is>
-          <t>IW582</t>
+          <t>IW197622</t>
         </is>
       </c>
       <c r="AI4" s="7" t="inlineStr">
@@ -3325,12 +3325,12 @@
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>IW528+</t>
+          <t>IW197244+</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>IW528</t>
+          <t>IW197244</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3342,12 +3342,12 @@
       <c r="N5" s="7" t="n"/>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>IW546+</t>
+          <t>IW197370+</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>IW546</t>
+          <t>IW197370</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -3359,12 +3359,12 @@
       <c r="T5" s="7" t="n"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>IW564+</t>
+          <t>IW197442+</t>
         </is>
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>IW564</t>
+          <t>IW197442</t>
         </is>
       </c>
       <c r="W5" s="7" t="inlineStr">
@@ -3376,12 +3376,12 @@
       <c r="AF5" s="7" t="n"/>
       <c r="AG5" s="7" t="inlineStr">
         <is>
-          <t>IW588+</t>
+          <t>IW197628+</t>
         </is>
       </c>
       <c r="AH5" s="7" t="inlineStr">
         <is>
-          <t>IW588</t>
+          <t>IW197628</t>
         </is>
       </c>
       <c r="AI5" s="7" t="inlineStr">
@@ -3395,12 +3395,12 @@
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>IW554+</t>
+          <t>IW197378+</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>IW554</t>
+          <t>IW197378</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
